--- a/r4-core-add-vbpk/StructureDefinition-at-core-patient.xlsx
+++ b/r4-core-add-vbpk/StructureDefinition-at-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T11:03:52+00:00</t>
+    <t>2026-06-12T11:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>90</v>
